--- a/aReport_card/2025_2026/Second_term/JSS2/Second_term_JSS2_Mathematics.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS2/Second_term_JSS2_Mathematics.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC9C2AC-FF32-46EC-8729-655EDA044A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38593AE-6A33-4A7C-9E29-676FA62287E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,13 +492,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>77</v>
@@ -512,13 +512,13 @@
         <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
         <v>76</v>
@@ -532,13 +532,13 @@
         <v>11</v>
       </c>
       <c r="C4" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>76</v>
@@ -552,13 +552,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
         <v>76</v>
@@ -575,10 +575,10 @@
         <v>33</v>
       </c>
       <c r="D6" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>76</v>
@@ -595,10 +595,10 @@
         <v>33</v>
       </c>
       <c r="D7" s="1">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
         <v>76</v>
@@ -615,10 +615,10 @@
         <v>34</v>
       </c>
       <c r="D8" s="1">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
         <v>77</v>
@@ -635,10 +635,10 @@
         <v>29</v>
       </c>
       <c r="D9" s="1">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
         <v>72</v>
